--- a/server/Database/사용자1주문.xlsx
+++ b/server/Database/사용자1주문.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -452,7 +452,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>마시멜로</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -461,7 +461,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -474,14 +474,66 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>버터스카치</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>누가</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>마시멜로</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>드롭스</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>1</v>
       </c>
     </row>

--- a/server/Database/사용자1주문.xlsx
+++ b/server/Database/사용자1주문.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마시멜로</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -461,11 +461,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -474,11 +474,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -487,11 +487,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -500,7 +500,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -526,14 +526,287 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>누가</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>태피</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>박하사탕</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>알사탕</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>캔디 케인</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>퍼지</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>구미</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>드롭스</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>박하사탕</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>버터스카치</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>알사탕</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>누가</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>태피</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>마시멜로</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>목캔디</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>4</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>드롭스</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>롤리팝</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>박하사탕</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>누룽지 사탕</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>계피사탕</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>캐러멜</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>누가</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>1</v>
       </c>
     </row>
